--- a/Data/2035/Trinity/Input/Xlsx/Node.xlsx
+++ b/Data/2035/Trinity/Input/Xlsx/Node.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C360"/>
+  <dimension ref="A1:C353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,4550 +547,4459 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>301559472.222463</v>
+        <v>48439611.11115</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>331057000.000265</v>
+        <v>51542972.222263</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>365656944.444737</v>
+        <v>55235055.5556</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>386773138.889198</v>
+        <v>57697083.333379</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>404279694.444768</v>
+        <v>59823555.555603</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>448670527.778137</v>
+        <v>63622750.000051</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>493588833.333728</v>
+        <v>67563250.000054</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>48439611.11115</v>
+        <v>2488427016.39088</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>51542972.222263</v>
+        <v>2667193077.779912</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>55235055.5556</v>
+        <v>2863872627.780069</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>57697083.333379</v>
+        <v>3049280476.11355</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>5</v>
       </c>
       <c r="C22" t="n">
-        <v>59823555.555603</v>
+        <v>3306327490.280423</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>6</v>
       </c>
       <c r="C23" t="n">
-        <v>63622750.000051</v>
+        <v>3733550617.225209</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>7</v>
       </c>
       <c r="C24" t="n">
-        <v>67563250.000054</v>
+        <v>4246458134.170063</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>2186867544.168416</v>
+        <v>6572409.692673</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>2336136077.779646</v>
+        <v>7026490.726115</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>2498215683.335332</v>
+        <v>7499127.62355</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>4</v>
       </c>
       <c r="C28" t="n">
-        <v>2662507337.224352</v>
+        <v>8128797.205142</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>2902047795.835655</v>
+        <v>9032125.547072999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>6</v>
       </c>
       <c r="C30" t="n">
-        <v>3284880089.447072</v>
+        <v>10313386.664093</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>7</v>
       </c>
       <c r="C31" t="n">
-        <v>3752869300.836335</v>
+        <v>12052201.719179</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES112</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>6572409.692673</v>
+        <v>6765610.92799</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES112</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>7026490.726115</v>
+        <v>7233040.036292</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES112</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>7499127.62355</v>
+        <v>7719570.47304</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES112</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>4</v>
       </c>
       <c r="C35" t="n">
-        <v>8128797.205142</v>
+        <v>8367749.695189</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES112</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>5</v>
       </c>
       <c r="C36" t="n">
-        <v>9032125.547072999</v>
+        <v>9297632.095634</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES112</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>6</v>
       </c>
       <c r="C37" t="n">
-        <v>10313386.664093</v>
+        <v>10616556.90712</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES112</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>7</v>
       </c>
       <c r="C38" t="n">
-        <v>12052201.719179</v>
+        <v>12406485.820339</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ES112</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>6765610.92799</v>
+        <v>1600009.429511</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ES112</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>7233040.036292</v>
+        <v>1710552.437211</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ES112</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>3</v>
       </c>
       <c r="C41" t="n">
-        <v>7719570.47304</v>
+        <v>1825612.746594</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ES112</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>4</v>
       </c>
       <c r="C42" t="n">
-        <v>8367749.695189</v>
+        <v>1978901.618581</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ES112</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>5</v>
       </c>
       <c r="C43" t="n">
-        <v>9297632.095634</v>
+        <v>2198810.89579</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ES112</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>6</v>
       </c>
       <c r="C44" t="n">
-        <v>10616556.90712</v>
+        <v>2510725.393631</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ES112</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>7</v>
       </c>
       <c r="C45" t="n">
-        <v>12406485.820339</v>
+        <v>2934028.354707</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES114</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>1600009.429511</v>
+        <v>4167492.007813</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES114</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>2</v>
       </c>
       <c r="C47" t="n">
-        <v>1710552.437211</v>
+        <v>4455419.749122</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES114</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>3</v>
       </c>
       <c r="C48" t="n">
-        <v>1825612.746594</v>
+        <v>4755113.557749</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES114</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>4</v>
       </c>
       <c r="C49" t="n">
-        <v>1978901.618581</v>
+        <v>5154380.047751</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES114</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>5</v>
       </c>
       <c r="C50" t="n">
-        <v>2198810.89579</v>
+        <v>5727170.519049</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES114</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>6</v>
       </c>
       <c r="C51" t="n">
-        <v>2510725.393631</v>
+        <v>6539603.966565</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES114</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>7</v>
       </c>
       <c r="C52" t="n">
-        <v>2934028.354707</v>
+        <v>7642167.285649</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ES114</t>
+          <t>ES120</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>4167492.007813</v>
+        <v>11730575.463768</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ES114</t>
+          <t>ES120</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>2</v>
       </c>
       <c r="C54" t="n">
-        <v>4455419.749122</v>
+        <v>12541028.871046</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ES114</t>
+          <t>ES120</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>3</v>
       </c>
       <c r="C55" t="n">
-        <v>4755113.557749</v>
+        <v>13384601.175813</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ES114</t>
+          <t>ES120</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>4</v>
       </c>
       <c r="C56" t="n">
-        <v>5154380.047751</v>
+        <v>14508448.727852</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ES114</t>
+          <t>ES120</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>5</v>
       </c>
       <c r="C57" t="n">
-        <v>5727170.519049</v>
+        <v>16120728.208147</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ES114</t>
+          <t>ES120</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>6</v>
       </c>
       <c r="C58" t="n">
-        <v>6539603.966565</v>
+        <v>18407550.077871</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ES114</t>
+          <t>ES120</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>7</v>
       </c>
       <c r="C59" t="n">
-        <v>7642167.285649</v>
+        <v>21511023.868306</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ES120</t>
+          <t>ES130</t>
         </is>
       </c>
       <c r="B60" t="n">
         <v>1</v>
       </c>
       <c r="C60" t="n">
-        <v>11730575.463768</v>
+        <v>4102244.168105</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ES120</t>
+          <t>ES130</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>2</v>
       </c>
       <c r="C61" t="n">
-        <v>12541028.871046</v>
+        <v>4385664.003201</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ES120</t>
+          <t>ES130</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>3</v>
       </c>
       <c r="C62" t="n">
-        <v>13384601.175813</v>
+        <v>4680665.691592</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ES120</t>
+          <t>ES130</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>4</v>
       </c>
       <c r="C63" t="n">
-        <v>14508448.727852</v>
+        <v>5073681.113591</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ES120</t>
+          <t>ES130</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>5</v>
       </c>
       <c r="C64" t="n">
-        <v>16120728.208147</v>
+        <v>5637503.759447</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ES120</t>
+          <t>ES130</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>6</v>
       </c>
       <c r="C65" t="n">
-        <v>18407550.077871</v>
+        <v>6437217.439952</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ES120</t>
+          <t>ES130</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>7</v>
       </c>
       <c r="C66" t="n">
-        <v>21511023.868306</v>
+        <v>7522518.608425</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ES130</t>
+          <t>ES211</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>1</v>
       </c>
       <c r="C67" t="n">
-        <v>4102244.168105</v>
+        <v>2989278.024264</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ES130</t>
+          <t>ES211</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>2</v>
       </c>
       <c r="C68" t="n">
-        <v>4385664.003201</v>
+        <v>3195804.171898</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ES130</t>
+          <t>ES211</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>3</v>
       </c>
       <c r="C69" t="n">
-        <v>4680665.691592</v>
+        <v>3410769.938949</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ES130</t>
+          <t>ES211</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>4</v>
       </c>
       <c r="C70" t="n">
-        <v>5073681.113591</v>
+        <v>3697157.661385</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ES130</t>
+          <t>ES211</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>5</v>
       </c>
       <c r="C71" t="n">
-        <v>5637503.759447</v>
+        <v>4108011.471098</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ES130</t>
+          <t>ES211</t>
         </is>
       </c>
       <c r="B72" t="n">
         <v>6</v>
       </c>
       <c r="C72" t="n">
-        <v>6437217.439952</v>
+        <v>4690757.50787</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ES130</t>
+          <t>ES211</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>7</v>
       </c>
       <c r="C73" t="n">
-        <v>7522518.608425</v>
+        <v>5481609.246498</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ES211</t>
+          <t>ES212</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>2989278.024264</v>
+        <v>6926485.965147</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ES211</t>
+          <t>ES212</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>2</v>
       </c>
       <c r="C75" t="n">
-        <v>3195804.171898</v>
+        <v>7405029.76449</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ES211</t>
+          <t>ES212</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>3</v>
       </c>
       <c r="C76" t="n">
-        <v>3410769.938949</v>
+        <v>7903129.090274</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ES211</t>
+          <t>ES212</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>4</v>
       </c>
       <c r="C77" t="n">
-        <v>3697157.661385</v>
+        <v>8566720.942199999</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ES211</t>
+          <t>ES212</t>
         </is>
       </c>
       <c r="B78" t="n">
         <v>5</v>
       </c>
       <c r="C78" t="n">
-        <v>4108011.471098</v>
+        <v>9518714.408049</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ES211</t>
+          <t>ES212</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>6</v>
       </c>
       <c r="C79" t="n">
-        <v>4690757.50787</v>
+        <v>10869001.069975</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ES211</t>
+          <t>ES212</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>7</v>
       </c>
       <c r="C80" t="n">
-        <v>5481609.246498</v>
+        <v>12701491.532105</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ES212</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B81" t="n">
         <v>1</v>
       </c>
       <c r="C81" t="n">
-        <v>6926485.965147</v>
+        <v>7630601.175583</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ES212</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>2</v>
       </c>
       <c r="C82" t="n">
-        <v>7405029.76449</v>
+        <v>8157791.571436</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ES212</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>3</v>
       </c>
       <c r="C83" t="n">
-        <v>7903129.090274</v>
+        <v>8706525.42003</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ES212</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>4</v>
       </c>
       <c r="C84" t="n">
-        <v>8566720.942199999</v>
+        <v>9437575.015869999</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ES212</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>5</v>
       </c>
       <c r="C85" t="n">
-        <v>9518714.408049</v>
+        <v>10486343.828253</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ES212</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>6</v>
       </c>
       <c r="C86" t="n">
-        <v>10869001.069975</v>
+        <v>11973894.520149</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ES212</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>7</v>
       </c>
       <c r="C87" t="n">
-        <v>12701491.532105</v>
+        <v>13992667.66788</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ES213</t>
+          <t>ES220</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>1</v>
       </c>
       <c r="C88" t="n">
-        <v>7630601.175583</v>
+        <v>6201549.163146</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ES213</t>
+          <t>ES220</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>2</v>
       </c>
       <c r="C89" t="n">
-        <v>8157791.571436</v>
+        <v>6630007.823609</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ES213</t>
+          <t>ES220</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>3</v>
       </c>
       <c r="C90" t="n">
-        <v>8706525.42003</v>
+        <v>7075975.298679</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ES213</t>
+          <t>ES220</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>4</v>
       </c>
       <c r="C91" t="n">
-        <v>9437575.015869999</v>
+        <v>7670114.594519</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ES213</t>
+          <t>ES220</t>
         </is>
       </c>
       <c r="B92" t="n">
         <v>5</v>
       </c>
       <c r="C92" t="n">
-        <v>10486343.828253</v>
+        <v>8522470.94248</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ES213</t>
+          <t>ES220</t>
         </is>
       </c>
       <c r="B93" t="n">
         <v>6</v>
       </c>
       <c r="C93" t="n">
-        <v>11973894.520149</v>
+        <v>9731434.500684001</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ES213</t>
+          <t>ES220</t>
         </is>
       </c>
       <c r="B94" t="n">
         <v>7</v>
       </c>
       <c r="C94" t="n">
-        <v>13992667.66788</v>
+        <v>11372133.658825</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ES220</t>
+          <t>ES230</t>
         </is>
       </c>
       <c r="B95" t="n">
         <v>1</v>
       </c>
       <c r="C95" t="n">
-        <v>6201549.163146</v>
+        <v>2484818.213293</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ES220</t>
+          <t>ES230</t>
         </is>
       </c>
       <c r="B96" t="n">
         <v>2</v>
       </c>
       <c r="C96" t="n">
-        <v>6630007.823609</v>
+        <v>2656491.750849</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ES220</t>
+          <t>ES230</t>
         </is>
       </c>
       <c r="B97" t="n">
         <v>3</v>
       </c>
       <c r="C97" t="n">
-        <v>7075975.298679</v>
+        <v>2835180.667995</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ES220</t>
+          <t>ES230</t>
         </is>
       </c>
       <c r="B98" t="n">
         <v>4</v>
       </c>
       <c r="C98" t="n">
-        <v>7670114.594519</v>
+        <v>3073238.628143</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ES220</t>
+          <t>ES230</t>
         </is>
       </c>
       <c r="B99" t="n">
         <v>5</v>
       </c>
       <c r="C99" t="n">
-        <v>8522470.94248</v>
+        <v>3414758.226216</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ES220</t>
+          <t>ES230</t>
         </is>
       </c>
       <c r="B100" t="n">
         <v>6</v>
       </c>
       <c r="C100" t="n">
-        <v>9731434.500684001</v>
+        <v>3899162.137175</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ES220</t>
+          <t>ES230</t>
         </is>
       </c>
       <c r="B101" t="n">
         <v>7</v>
       </c>
       <c r="C101" t="n">
-        <v>11372133.658825</v>
+        <v>4556552.58002</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ES230</t>
+          <t>ES241</t>
         </is>
       </c>
       <c r="B102" t="n">
         <v>1</v>
       </c>
       <c r="C102" t="n">
-        <v>2484818.213293</v>
+        <v>1540754.06639</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ES230</t>
+          <t>ES241</t>
         </is>
       </c>
       <c r="B103" t="n">
         <v>2</v>
       </c>
       <c r="C103" t="n">
-        <v>2656491.750849</v>
+        <v>1647203.18193</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ES230</t>
+          <t>ES241</t>
         </is>
       </c>
       <c r="B104" t="n">
         <v>3</v>
       </c>
       <c r="C104" t="n">
-        <v>2835180.667995</v>
+        <v>1758002.303667</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ES230</t>
+          <t>ES241</t>
         </is>
       </c>
       <c r="B105" t="n">
         <v>4</v>
       </c>
       <c r="C105" t="n">
-        <v>3073238.628143</v>
+        <v>1905614.216753</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ES230</t>
+          <t>ES241</t>
         </is>
       </c>
       <c r="B106" t="n">
         <v>5</v>
       </c>
       <c r="C106" t="n">
-        <v>3414758.226216</v>
+        <v>2117379.289413</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ES230</t>
+          <t>ES241</t>
         </is>
       </c>
       <c r="B107" t="n">
         <v>6</v>
       </c>
       <c r="C107" t="n">
-        <v>3899162.137175</v>
+        <v>2417742.226062</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ES230</t>
+          <t>ES241</t>
         </is>
       </c>
       <c r="B108" t="n">
         <v>7</v>
       </c>
       <c r="C108" t="n">
-        <v>4556552.58002</v>
+        <v>2825368.422861</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ES241</t>
+          <t>ES242</t>
         </is>
       </c>
       <c r="B109" t="n">
         <v>1</v>
       </c>
       <c r="C109" t="n">
-        <v>1540754.06639</v>
+        <v>778478.870999</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ES241</t>
+          <t>ES242</t>
         </is>
       </c>
       <c r="B110" t="n">
         <v>2</v>
       </c>
       <c r="C110" t="n">
-        <v>1647203.18193</v>
+        <v>832263.176419</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ES241</t>
+          <t>ES242</t>
         </is>
       </c>
       <c r="B111" t="n">
         <v>3</v>
       </c>
       <c r="C111" t="n">
-        <v>1758002.303667</v>
+        <v>888245.3588320001</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ES241</t>
+          <t>ES242</t>
         </is>
       </c>
       <c r="B112" t="n">
         <v>4</v>
       </c>
       <c r="C112" t="n">
-        <v>1905614.216753</v>
+        <v>962827.511787</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ES241</t>
+          <t>ES242</t>
         </is>
       </c>
       <c r="B113" t="n">
         <v>5</v>
       </c>
       <c r="C113" t="n">
-        <v>2117379.289413</v>
+        <v>1069823.584864</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ES241</t>
+          <t>ES242</t>
         </is>
       </c>
       <c r="B114" t="n">
         <v>6</v>
       </c>
       <c r="C114" t="n">
-        <v>2417742.226062</v>
+        <v>1221584.469299</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ES241</t>
+          <t>ES242</t>
         </is>
       </c>
       <c r="B115" t="n">
         <v>7</v>
       </c>
       <c r="C115" t="n">
-        <v>2825368.422861</v>
+        <v>1427541.012524</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ES242</t>
+          <t>ES243</t>
         </is>
       </c>
       <c r="B116" t="n">
         <v>1</v>
       </c>
       <c r="C116" t="n">
-        <v>778478.870999</v>
+        <v>9162737.996452</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ES242</t>
+          <t>ES243</t>
         </is>
       </c>
       <c r="B117" t="n">
         <v>2</v>
       </c>
       <c r="C117" t="n">
-        <v>832263.176419</v>
+        <v>9795782.151205</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ES242</t>
+          <t>ES243</t>
         </is>
       </c>
       <c r="B118" t="n">
         <v>3</v>
       </c>
       <c r="C118" t="n">
-        <v>888245.3588320001</v>
+        <v>10454695.435853</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ES242</t>
+          <t>ES243</t>
         </is>
       </c>
       <c r="B119" t="n">
         <v>4</v>
       </c>
       <c r="C119" t="n">
-        <v>962827.511787</v>
+        <v>11332531.369741</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ES242</t>
+          <t>ES243</t>
         </is>
       </c>
       <c r="B120" t="n">
         <v>5</v>
       </c>
       <c r="C120" t="n">
-        <v>1069823.584864</v>
+        <v>12591880.879118</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ES242</t>
+          <t>ES243</t>
         </is>
       </c>
       <c r="B121" t="n">
         <v>6</v>
       </c>
       <c r="C121" t="n">
-        <v>1221584.469299</v>
+        <v>14378114.615183</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ES242</t>
+          <t>ES243</t>
         </is>
       </c>
       <c r="B122" t="n">
         <v>7</v>
       </c>
       <c r="C122" t="n">
-        <v>1427541.012524</v>
+        <v>16802234.157182</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ES243</t>
+          <t>ES300</t>
         </is>
       </c>
       <c r="B123" t="n">
         <v>1</v>
       </c>
       <c r="C123" t="n">
-        <v>9162737.996452</v>
+        <v>37689532.453736</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ES243</t>
+          <t>ES300</t>
         </is>
       </c>
       <c r="B124" t="n">
         <v>2</v>
       </c>
       <c r="C124" t="n">
-        <v>9795782.151205</v>
+        <v>40293463.530279</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ES243</t>
+          <t>ES300</t>
         </is>
       </c>
       <c r="B125" t="n">
         <v>3</v>
       </c>
       <c r="C125" t="n">
-        <v>10454695.435853</v>
+        <v>43003803.347435</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ES243</t>
+          <t>ES300</t>
         </is>
       </c>
       <c r="B126" t="n">
         <v>4</v>
       </c>
       <c r="C126" t="n">
-        <v>11332531.369741</v>
+        <v>46614648.264331</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ES243</t>
+          <t>ES300</t>
         </is>
       </c>
       <c r="B127" t="n">
         <v>5</v>
       </c>
       <c r="C127" t="n">
-        <v>12591880.879118</v>
+        <v>51794791.385591</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ES243</t>
+          <t>ES300</t>
         </is>
       </c>
       <c r="B128" t="n">
         <v>6</v>
       </c>
       <c r="C128" t="n">
-        <v>14378114.615183</v>
+        <v>59142192.827327</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ES243</t>
+          <t>ES300</t>
         </is>
       </c>
       <c r="B129" t="n">
         <v>7</v>
       </c>
       <c r="C129" t="n">
-        <v>16802234.157182</v>
+        <v>69113440.743103</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ES300</t>
+          <t>ES412</t>
         </is>
       </c>
       <c r="B130" t="n">
         <v>1</v>
       </c>
       <c r="C130" t="n">
-        <v>37689532.453736</v>
+        <v>3143930.369393</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ES300</t>
+          <t>ES412</t>
         </is>
       </c>
       <c r="B131" t="n">
         <v>2</v>
       </c>
       <c r="C131" t="n">
-        <v>40293463.530279</v>
+        <v>3361141.288669</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ES300</t>
+          <t>ES412</t>
         </is>
       </c>
       <c r="B132" t="n">
         <v>3</v>
       </c>
       <c r="C132" t="n">
-        <v>43003803.347435</v>
+        <v>3587228.45685</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ES300</t>
+          <t>ES412</t>
         </is>
       </c>
       <c r="B133" t="n">
         <v>4</v>
       </c>
       <c r="C133" t="n">
-        <v>46614648.264331</v>
+        <v>3888432.644175</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ES300</t>
+          <t>ES412</t>
         </is>
       </c>
       <c r="B134" t="n">
         <v>5</v>
       </c>
       <c r="C134" t="n">
-        <v>51794791.385591</v>
+        <v>4320542.257016</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ES300</t>
+          <t>ES412</t>
         </is>
       </c>
       <c r="B135" t="n">
         <v>6</v>
       </c>
       <c r="C135" t="n">
-        <v>59142192.827327</v>
+        <v>4933437.058966</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ES300</t>
+          <t>ES412</t>
         </is>
       </c>
       <c r="B136" t="n">
         <v>7</v>
       </c>
       <c r="C136" t="n">
-        <v>69113440.743103</v>
+        <v>5765204.053731</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ES412</t>
+          <t>ES413</t>
         </is>
       </c>
       <c r="B137" t="n">
         <v>1</v>
       </c>
       <c r="C137" t="n">
-        <v>3143930.369393</v>
+        <v>3109946.906565</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ES412</t>
+          <t>ES413</t>
         </is>
       </c>
       <c r="B138" t="n">
         <v>2</v>
       </c>
       <c r="C138" t="n">
-        <v>3361141.288669</v>
+        <v>3324809.943307</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ES412</t>
+          <t>ES413</t>
         </is>
       </c>
       <c r="B139" t="n">
         <v>3</v>
       </c>
       <c r="C139" t="n">
-        <v>3587228.45685</v>
+        <v>3548453.283549</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ES412</t>
+          <t>ES413</t>
         </is>
       </c>
       <c r="B140" t="n">
         <v>4</v>
       </c>
       <c r="C140" t="n">
-        <v>3888432.644175</v>
+        <v>3846401.685885</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ES412</t>
+          <t>ES413</t>
         </is>
       </c>
       <c r="B141" t="n">
         <v>5</v>
       </c>
       <c r="C141" t="n">
-        <v>4320542.257016</v>
+        <v>4273840.527035</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ES412</t>
+          <t>ES413</t>
         </is>
       </c>
       <c r="B142" t="n">
         <v>6</v>
       </c>
       <c r="C142" t="n">
-        <v>4933437.058966</v>
+        <v>4880110.408814</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ES412</t>
+          <t>ES413</t>
         </is>
       </c>
       <c r="B143" t="n">
         <v>7</v>
       </c>
       <c r="C143" t="n">
-        <v>5765204.053731</v>
+        <v>5702886.643789</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ES413</t>
+          <t>ES414</t>
         </is>
       </c>
       <c r="B144" t="n">
         <v>1</v>
       </c>
       <c r="C144" t="n">
-        <v>3109946.906565</v>
+        <v>1798082.443882</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ES413</t>
+          <t>ES414</t>
         </is>
       </c>
       <c r="B145" t="n">
         <v>2</v>
       </c>
       <c r="C145" t="n">
-        <v>3324809.943307</v>
+        <v>1922310.112654</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ES413</t>
+          <t>ES414</t>
         </is>
       </c>
       <c r="B146" t="n">
         <v>3</v>
       </c>
       <c r="C146" t="n">
-        <v>3548453.283549</v>
+        <v>2051614.302037</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ES413</t>
+          <t>ES414</t>
         </is>
       </c>
       <c r="B147" t="n">
         <v>4</v>
       </c>
       <c r="C147" t="n">
-        <v>3846401.685885</v>
+        <v>2223879.555278</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ES413</t>
+          <t>ES414</t>
         </is>
       </c>
       <c r="B148" t="n">
         <v>5</v>
       </c>
       <c r="C148" t="n">
-        <v>4273840.527035</v>
+        <v>2471012.480436</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ES413</t>
+          <t>ES414</t>
         </is>
       </c>
       <c r="B149" t="n">
         <v>6</v>
       </c>
       <c r="C149" t="n">
-        <v>4880110.408814</v>
+        <v>2821540.403719</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ES413</t>
+          <t>ES414</t>
         </is>
       </c>
       <c r="B150" t="n">
         <v>7</v>
       </c>
       <c r="C150" t="n">
-        <v>5702886.643789</v>
+        <v>3297246.114395</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ES414</t>
+          <t>ES415</t>
         </is>
       </c>
       <c r="B151" t="n">
         <v>1</v>
       </c>
       <c r="C151" t="n">
-        <v>1798082.443882</v>
+        <v>1638531.304159</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ES414</t>
+          <t>ES415</t>
         </is>
       </c>
       <c r="B152" t="n">
         <v>2</v>
       </c>
       <c r="C152" t="n">
-        <v>1922310.112654</v>
+        <v>1751735.748604</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ES414</t>
+          <t>ES415</t>
         </is>
       </c>
       <c r="B153" t="n">
         <v>3</v>
       </c>
       <c r="C153" t="n">
-        <v>2051614.302037</v>
+        <v>1869566.25342</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ES414</t>
+          <t>ES415</t>
         </is>
       </c>
       <c r="B154" t="n">
         <v>4</v>
       </c>
       <c r="C154" t="n">
-        <v>2223879.555278</v>
+        <v>2026545.712851</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ES414</t>
+          <t>ES415</t>
         </is>
       </c>
       <c r="B155" t="n">
         <v>5</v>
       </c>
       <c r="C155" t="n">
-        <v>2471012.480436</v>
+        <v>2251749.532363</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ES414</t>
+          <t>ES415</t>
         </is>
       </c>
       <c r="B156" t="n">
         <v>6</v>
       </c>
       <c r="C156" t="n">
-        <v>2821540.403719</v>
+        <v>2571173.692939</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ES414</t>
+          <t>ES415</t>
         </is>
       </c>
       <c r="B157" t="n">
         <v>7</v>
       </c>
       <c r="C157" t="n">
-        <v>3297246.114395</v>
+        <v>3004668.108705</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ES415</t>
+          <t>ES416</t>
         </is>
       </c>
       <c r="B158" t="n">
         <v>1</v>
       </c>
       <c r="C158" t="n">
-        <v>1638531.304159</v>
+        <v>1866082.838741</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ES415</t>
+          <t>ES416</t>
         </is>
       </c>
       <c r="B159" t="n">
         <v>2</v>
       </c>
       <c r="C159" t="n">
-        <v>1751735.748604</v>
+        <v>1995008.584932</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ES415</t>
+          <t>ES416</t>
         </is>
       </c>
       <c r="B160" t="n">
         <v>3</v>
       </c>
       <c r="C160" t="n">
-        <v>1869566.25342</v>
+        <v>2129202.837041</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ES415</t>
+          <t>ES416</t>
         </is>
       </c>
       <c r="B161" t="n">
         <v>4</v>
       </c>
       <c r="C161" t="n">
-        <v>2026545.712851</v>
+        <v>2307982.866776</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ES415</t>
+          <t>ES416</t>
         </is>
       </c>
       <c r="B162" t="n">
         <v>5</v>
       </c>
       <c r="C162" t="n">
-        <v>2251749.532363</v>
+        <v>2564461.935405</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ES415</t>
+          <t>ES416</t>
         </is>
       </c>
       <c r="B163" t="n">
         <v>6</v>
       </c>
       <c r="C163" t="n">
-        <v>2571173.692939</v>
+        <v>2928246.223698</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ES415</t>
+          <t>ES416</t>
         </is>
       </c>
       <c r="B164" t="n">
         <v>7</v>
       </c>
       <c r="C164" t="n">
-        <v>3004668.108705</v>
+        <v>3421942.30866</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ES416</t>
+          <t>ES417</t>
         </is>
       </c>
       <c r="B165" t="n">
         <v>1</v>
       </c>
       <c r="C165" t="n">
-        <v>1866082.838741</v>
+        <v>820278.37082</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ES416</t>
+          <t>ES417</t>
         </is>
       </c>
       <c r="B166" t="n">
         <v>2</v>
       </c>
       <c r="C166" t="n">
-        <v>1995008.584932</v>
+        <v>876950.560739</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ES416</t>
+          <t>ES417</t>
         </is>
       </c>
       <c r="B167" t="n">
         <v>3</v>
       </c>
       <c r="C167" t="n">
-        <v>2129202.837041</v>
+        <v>935938.64005</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ES416</t>
+          <t>ES417</t>
         </is>
       </c>
       <c r="B168" t="n">
         <v>4</v>
       </c>
       <c r="C168" t="n">
-        <v>2307982.866776</v>
+        <v>1014525.393265</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ES416</t>
+          <t>ES417</t>
         </is>
       </c>
       <c r="B169" t="n">
         <v>5</v>
       </c>
       <c r="C169" t="n">
-        <v>2564461.935405</v>
+        <v>1127266.493604</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ES416</t>
+          <t>ES417</t>
         </is>
       </c>
       <c r="B170" t="n">
         <v>6</v>
       </c>
       <c r="C170" t="n">
-        <v>2928246.223698</v>
+        <v>1287175.998764</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ES416</t>
+          <t>ES417</t>
         </is>
       </c>
       <c r="B171" t="n">
         <v>7</v>
       </c>
       <c r="C171" t="n">
-        <v>3421942.30866</v>
+        <v>1504191.134344</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ES417</t>
+          <t>ES418</t>
         </is>
       </c>
       <c r="B172" t="n">
         <v>1</v>
       </c>
       <c r="C172" t="n">
-        <v>820278.37082</v>
+        <v>4024133.101705</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ES417</t>
+          <t>ES418</t>
         </is>
       </c>
       <c r="B173" t="n">
         <v>2</v>
       </c>
       <c r="C173" t="n">
-        <v>876950.560739</v>
+        <v>4302156.323472</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ES417</t>
+          <t>ES418</t>
         </is>
       </c>
       <c r="B174" t="n">
         <v>3</v>
       </c>
       <c r="C174" t="n">
-        <v>935938.64005</v>
+        <v>4591540.867801</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ES417</t>
+          <t>ES418</t>
         </is>
       </c>
       <c r="B175" t="n">
         <v>4</v>
       </c>
       <c r="C175" t="n">
-        <v>1014525.393265</v>
+        <v>4977072.860617</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ES417</t>
+          <t>ES418</t>
         </is>
       </c>
       <c r="B176" t="n">
         <v>5</v>
       </c>
       <c r="C176" t="n">
-        <v>1127266.493604</v>
+        <v>5530159.727148</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ES417</t>
+          <t>ES418</t>
         </is>
       </c>
       <c r="B177" t="n">
         <v>6</v>
       </c>
       <c r="C177" t="n">
-        <v>1287175.998764</v>
+        <v>6314646.013612</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ES417</t>
+          <t>ES418</t>
         </is>
       </c>
       <c r="B178" t="n">
         <v>7</v>
       </c>
       <c r="C178" t="n">
-        <v>1504191.134344</v>
+        <v>7379281.900311</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ES418</t>
+          <t>ES419</t>
         </is>
       </c>
       <c r="B179" t="n">
         <v>1</v>
       </c>
       <c r="C179" t="n">
-        <v>4024133.101705</v>
+        <v>822738.3335600001</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ES418</t>
+          <t>ES419</t>
         </is>
       </c>
       <c r="B180" t="n">
         <v>2</v>
       </c>
       <c r="C180" t="n">
-        <v>4302156.323472</v>
+        <v>879580.479778</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ES418</t>
+          <t>ES419</t>
         </is>
       </c>
       <c r="B181" t="n">
         <v>3</v>
       </c>
       <c r="C181" t="n">
-        <v>4591540.867801</v>
+        <v>938745.4605930001</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ES418</t>
+          <t>ES419</t>
         </is>
       </c>
       <c r="B182" t="n">
         <v>4</v>
       </c>
       <c r="C182" t="n">
-        <v>4977072.860617</v>
+        <v>1017567.890489</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ES418</t>
+          <t>ES419</t>
         </is>
       </c>
       <c r="B183" t="n">
         <v>5</v>
       </c>
       <c r="C183" t="n">
-        <v>5530159.727148</v>
+        <v>1130647.094229</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ES418</t>
+          <t>ES419</t>
         </is>
       </c>
       <c r="B184" t="n">
         <v>6</v>
       </c>
       <c r="C184" t="n">
-        <v>6314646.013612</v>
+        <v>1291036.157839</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ES418</t>
+          <t>ES419</t>
         </is>
       </c>
       <c r="B185" t="n">
         <v>7</v>
       </c>
       <c r="C185" t="n">
-        <v>7379281.900311</v>
+        <v>1508702.108029</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ES419</t>
+          <t>ES421</t>
         </is>
       </c>
       <c r="B186" t="n">
         <v>1</v>
       </c>
       <c r="C186" t="n">
-        <v>822738.3335600001</v>
+        <v>1476298.830108</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ES419</t>
+          <t>ES421</t>
         </is>
       </c>
       <c r="B187" t="n">
         <v>2</v>
       </c>
       <c r="C187" t="n">
-        <v>879580.479778</v>
+        <v>1578294.799591</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ES419</t>
+          <t>ES421</t>
         </is>
       </c>
       <c r="B188" t="n">
         <v>3</v>
       </c>
       <c r="C188" t="n">
-        <v>938745.4605930001</v>
+        <v>1684458.799004</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ES419</t>
+          <t>ES421</t>
         </is>
       </c>
       <c r="B189" t="n">
         <v>4</v>
       </c>
       <c r="C189" t="n">
-        <v>1017567.890489</v>
+        <v>1825895.579443</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ES419</t>
+          <t>ES421</t>
         </is>
       </c>
       <c r="B190" t="n">
         <v>5</v>
       </c>
       <c r="C190" t="n">
-        <v>1130647.094229</v>
+        <v>2028801.764047</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ES419</t>
+          <t>ES421</t>
         </is>
       </c>
       <c r="B191" t="n">
         <v>6</v>
       </c>
       <c r="C191" t="n">
-        <v>1291036.157839</v>
+        <v>2316599.448088</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ES419</t>
+          <t>ES421</t>
         </is>
       </c>
       <c r="B192" t="n">
         <v>7</v>
       </c>
       <c r="C192" t="n">
-        <v>1508702.108029</v>
+        <v>2707173.187649</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ES421</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B193" t="n">
         <v>1</v>
       </c>
       <c r="C193" t="n">
-        <v>1476298.830108</v>
+        <v>3939375.349611</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ES421</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B194" t="n">
         <v>2</v>
       </c>
       <c r="C194" t="n">
-        <v>1578294.799591</v>
+        <v>4211542.745362</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>ES421</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B195" t="n">
         <v>3</v>
       </c>
       <c r="C195" t="n">
-        <v>1684458.799004</v>
+        <v>4494832.167376</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>ES421</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B196" t="n">
         <v>4</v>
       </c>
       <c r="C196" t="n">
-        <v>1825895.579443</v>
+        <v>4872243.945416</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>ES421</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B197" t="n">
         <v>5</v>
       </c>
       <c r="C197" t="n">
-        <v>2028801.764047</v>
+        <v>5413681.495601</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ES421</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B198" t="n">
         <v>6</v>
       </c>
       <c r="C198" t="n">
-        <v>2316599.448088</v>
+        <v>6181644.647142</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ES421</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B199" t="n">
         <v>7</v>
       </c>
       <c r="C199" t="n">
-        <v>2707173.187649</v>
+        <v>7223856.786347</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES423</t>
         </is>
       </c>
       <c r="B200" t="n">
         <v>1</v>
       </c>
       <c r="C200" t="n">
-        <v>3939375.349611</v>
+        <v>1350732.789115</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES423</t>
         </is>
       </c>
       <c r="B201" t="n">
         <v>2</v>
       </c>
       <c r="C201" t="n">
-        <v>4211542.745362</v>
+        <v>1444053.529827</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES423</t>
         </is>
       </c>
       <c r="B202" t="n">
         <v>3</v>
       </c>
       <c r="C202" t="n">
-        <v>4494832.167376</v>
+        <v>1541187.790253</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES423</t>
         </is>
       </c>
       <c r="B203" t="n">
         <v>4</v>
       </c>
       <c r="C203" t="n">
-        <v>4872243.945416</v>
+        <v>1670594.7186</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES423</t>
         </is>
       </c>
       <c r="B204" t="n">
         <v>5</v>
       </c>
       <c r="C204" t="n">
-        <v>5413681.495601</v>
+        <v>1856242.794091</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES423</t>
         </is>
       </c>
       <c r="B205" t="n">
         <v>6</v>
       </c>
       <c r="C205" t="n">
-        <v>6181644.647142</v>
+        <v>2119561.954505</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES423</t>
         </is>
       </c>
       <c r="B206" t="n">
         <v>7</v>
       </c>
       <c r="C206" t="n">
-        <v>7223856.786347</v>
+        <v>2476915.591746</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ES423</t>
+          <t>ES424</t>
         </is>
       </c>
       <c r="B207" t="n">
         <v>1</v>
       </c>
       <c r="C207" t="n">
-        <v>1350732.789115</v>
+        <v>727120.642204</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>ES423</t>
+          <t>ES424</t>
         </is>
       </c>
       <c r="B208" t="n">
         <v>2</v>
       </c>
       <c r="C208" t="n">
-        <v>1444053.529827</v>
+        <v>777356.66036</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ES423</t>
+          <t>ES424</t>
         </is>
       </c>
       <c r="B209" t="n">
         <v>3</v>
       </c>
       <c r="C209" t="n">
-        <v>1541187.790253</v>
+        <v>829645.5559799999</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ES423</t>
+          <t>ES424</t>
         </is>
       </c>
       <c r="B210" t="n">
         <v>4</v>
       </c>
       <c r="C210" t="n">
-        <v>1670594.7186</v>
+        <v>899307.334833</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ES423</t>
+          <t>ES424</t>
         </is>
       </c>
       <c r="B211" t="n">
         <v>5</v>
       </c>
       <c r="C211" t="n">
-        <v>1856242.794091</v>
+        <v>999244.605153</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ES423</t>
+          <t>ES424</t>
         </is>
       </c>
       <c r="B212" t="n">
         <v>6</v>
       </c>
       <c r="C212" t="n">
-        <v>2119561.954505</v>
+        <v>1140993.438504</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ES423</t>
+          <t>ES424</t>
         </is>
       </c>
       <c r="B213" t="n">
         <v>7</v>
       </c>
       <c r="C213" t="n">
-        <v>2476915.591746</v>
+        <v>1333362.505352</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ES424</t>
+          <t>ES425</t>
         </is>
       </c>
       <c r="B214" t="n">
         <v>1</v>
       </c>
       <c r="C214" t="n">
-        <v>727120.642204</v>
+        <v>3429386.936679</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ES424</t>
+          <t>ES425</t>
         </is>
       </c>
       <c r="B215" t="n">
         <v>2</v>
       </c>
       <c r="C215" t="n">
-        <v>777356.66036</v>
+        <v>3666319.756922</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ES424</t>
+          <t>ES425</t>
         </is>
       </c>
       <c r="B216" t="n">
         <v>3</v>
       </c>
       <c r="C216" t="n">
-        <v>829645.5559799999</v>
+        <v>3912934.754715</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ES424</t>
+          <t>ES425</t>
         </is>
       </c>
       <c r="B217" t="n">
         <v>4</v>
       </c>
       <c r="C217" t="n">
-        <v>899307.334833</v>
+        <v>4241487.102866</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>ES424</t>
+          <t>ES425</t>
         </is>
       </c>
       <c r="B218" t="n">
         <v>5</v>
       </c>
       <c r="C218" t="n">
-        <v>999244.605153</v>
+        <v>4712830.5766</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ES424</t>
+          <t>ES425</t>
         </is>
       </c>
       <c r="B219" t="n">
         <v>6</v>
       </c>
       <c r="C219" t="n">
-        <v>1140993.438504</v>
+        <v>5381373.826739</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ES424</t>
+          <t>ES425</t>
         </is>
       </c>
       <c r="B220" t="n">
         <v>7</v>
       </c>
       <c r="C220" t="n">
-        <v>1333362.505352</v>
+        <v>6288662.007793</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ES425</t>
+          <t>ES431</t>
         </is>
       </c>
       <c r="B221" t="n">
         <v>1</v>
       </c>
       <c r="C221" t="n">
-        <v>3429386.936679</v>
+        <v>2946851.499656</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>ES425</t>
+          <t>ES431</t>
         </is>
       </c>
       <c r="B222" t="n">
         <v>2</v>
       </c>
       <c r="C222" t="n">
-        <v>3666319.756922</v>
+        <v>3150446.442292</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ES425</t>
+          <t>ES431</t>
         </is>
       </c>
       <c r="B223" t="n">
         <v>3</v>
       </c>
       <c r="C223" t="n">
-        <v>3912934.754715</v>
+        <v>3362361.22167</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>ES425</t>
+          <t>ES431</t>
         </is>
       </c>
       <c r="B224" t="n">
         <v>4</v>
       </c>
       <c r="C224" t="n">
-        <v>4241487.102866</v>
+        <v>3644684.271748</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>ES425</t>
+          <t>ES431</t>
         </is>
       </c>
       <c r="B225" t="n">
         <v>5</v>
       </c>
       <c r="C225" t="n">
-        <v>4712830.5766</v>
+        <v>4049706.874352</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>ES425</t>
+          <t>ES431</t>
         </is>
       </c>
       <c r="B226" t="n">
         <v>6</v>
       </c>
       <c r="C226" t="n">
-        <v>5381373.826739</v>
+        <v>4624182.054794</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>ES425</t>
+          <t>ES431</t>
         </is>
       </c>
       <c r="B227" t="n">
         <v>7</v>
       </c>
       <c r="C227" t="n">
-        <v>6288662.007793</v>
+        <v>5403809.313639</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>ES431</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="B228" t="n">
         <v>1</v>
       </c>
       <c r="C228" t="n">
-        <v>2946851.499656</v>
+        <v>1418585.744817</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>ES431</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="B229" t="n">
         <v>2</v>
       </c>
       <c r="C229" t="n">
-        <v>3150446.442292</v>
+        <v>1516594.376529</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>ES431</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="B230" t="n">
         <v>3</v>
       </c>
       <c r="C230" t="n">
-        <v>3362361.22167</v>
+        <v>1618608.096995</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>ES431</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="B231" t="n">
         <v>4</v>
       </c>
       <c r="C231" t="n">
-        <v>3644684.271748</v>
+        <v>1754515.676431</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>ES431</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="B232" t="n">
         <v>5</v>
       </c>
       <c r="C232" t="n">
-        <v>4049706.874352</v>
+        <v>1949489.630989</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>ES431</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="B233" t="n">
         <v>6</v>
       </c>
       <c r="C233" t="n">
-        <v>4624182.054794</v>
+        <v>2226036.413825</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>ES431</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="B234" t="n">
         <v>7</v>
       </c>
       <c r="C234" t="n">
-        <v>5403809.313639</v>
+        <v>2601341.418437</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>ES511</t>
         </is>
       </c>
       <c r="B235" t="n">
         <v>1</v>
       </c>
       <c r="C235" t="n">
-        <v>1418585.744817</v>
+        <v>35654977.986107</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>ES511</t>
         </is>
       </c>
       <c r="B236" t="n">
         <v>2</v>
       </c>
       <c r="C236" t="n">
-        <v>1516594.376529</v>
+        <v>38118343.784699</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>ES511</t>
         </is>
       </c>
       <c r="B237" t="n">
         <v>3</v>
       </c>
       <c r="C237" t="n">
-        <v>1618608.096995</v>
+        <v>40682374.172558</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>ES511</t>
         </is>
       </c>
       <c r="B238" t="n">
         <v>4</v>
       </c>
       <c r="C238" t="n">
-        <v>1754515.676431</v>
+        <v>44098298.63862</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>ES511</t>
         </is>
       </c>
       <c r="B239" t="n">
         <v>5</v>
       </c>
       <c r="C239" t="n">
-        <v>1949489.630989</v>
+        <v>48998807.531378</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>ES511</t>
         </is>
       </c>
       <c r="B240" t="n">
         <v>6</v>
       </c>
       <c r="C240" t="n">
-        <v>2226036.413825</v>
+        <v>55949581.913675</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>ES511</t>
         </is>
       </c>
       <c r="B241" t="n">
         <v>7</v>
       </c>
       <c r="C241" t="n">
-        <v>2601341.418437</v>
+        <v>65382562.420063</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>ES511</t>
+          <t>ES512</t>
         </is>
       </c>
       <c r="B242" t="n">
         <v>1</v>
       </c>
       <c r="C242" t="n">
-        <v>35654977.986107</v>
+        <v>4105512.642085</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>ES511</t>
+          <t>ES512</t>
         </is>
       </c>
       <c r="B243" t="n">
         <v>2</v>
       </c>
       <c r="C243" t="n">
-        <v>38118343.784699</v>
+        <v>4389158.292691</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>ES511</t>
+          <t>ES512</t>
         </is>
       </c>
       <c r="B244" t="n">
         <v>3</v>
       </c>
       <c r="C244" t="n">
-        <v>40682374.172558</v>
+        <v>4684395.024463</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>ES511</t>
+          <t>ES512</t>
         </is>
       </c>
       <c r="B245" t="n">
         <v>4</v>
       </c>
       <c r="C245" t="n">
-        <v>44098298.63862</v>
+        <v>5077723.582548</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>ES511</t>
+          <t>ES512</t>
         </is>
       </c>
       <c r="B246" t="n">
         <v>5</v>
       </c>
       <c r="C246" t="n">
-        <v>48998807.531378</v>
+        <v>5641995.455601</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>ES511</t>
+          <t>ES512</t>
         </is>
       </c>
       <c r="B247" t="n">
         <v>6</v>
       </c>
       <c r="C247" t="n">
-        <v>55949581.913675</v>
+        <v>6442346.310113</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>ES511</t>
+          <t>ES512</t>
         </is>
       </c>
       <c r="B248" t="n">
         <v>7</v>
       </c>
       <c r="C248" t="n">
-        <v>65382562.420063</v>
+        <v>7528512.195186</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>ES512</t>
+          <t>ES513</t>
         </is>
       </c>
       <c r="B249" t="n">
         <v>1</v>
       </c>
       <c r="C249" t="n">
-        <v>4105512.642085</v>
+        <v>3693203.546005</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>ES512</t>
+          <t>ES513</t>
         </is>
       </c>
       <c r="B250" t="n">
         <v>2</v>
       </c>
       <c r="C250" t="n">
-        <v>4389158.292691</v>
+        <v>3948363.184752</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>ES512</t>
+          <t>ES513</t>
         </is>
       </c>
       <c r="B251" t="n">
         <v>3</v>
       </c>
       <c r="C251" t="n">
-        <v>4684395.024463</v>
+        <v>4213949.833669</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>ES512</t>
+          <t>ES513</t>
         </is>
       </c>
       <c r="B252" t="n">
         <v>4</v>
       </c>
       <c r="C252" t="n">
-        <v>5077723.582548</v>
+        <v>4567777.126897</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>ES512</t>
+          <t>ES513</t>
         </is>
       </c>
       <c r="B253" t="n">
         <v>5</v>
       </c>
       <c r="C253" t="n">
-        <v>5641995.455601</v>
+        <v>5075380.211858</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>ES512</t>
+          <t>ES513</t>
         </is>
       </c>
       <c r="B254" t="n">
         <v>6</v>
       </c>
       <c r="C254" t="n">
-        <v>6442346.310113</v>
+        <v>5795353.29966</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>ES512</t>
+          <t>ES513</t>
         </is>
       </c>
       <c r="B255" t="n">
         <v>7</v>
       </c>
       <c r="C255" t="n">
-        <v>7528512.195186</v>
+        <v>6772437.539319</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>ES513</t>
+          <t>ES514</t>
         </is>
       </c>
       <c r="B256" t="n">
         <v>1</v>
       </c>
       <c r="C256" t="n">
-        <v>3693203.546005</v>
+        <v>7229025.88703</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>ES513</t>
+          <t>ES514</t>
         </is>
       </c>
       <c r="B257" t="n">
         <v>2</v>
       </c>
       <c r="C257" t="n">
-        <v>3948363.184752</v>
+        <v>7728471.858759</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>ES513</t>
+          <t>ES514</t>
         </is>
       </c>
       <c r="B258" t="n">
         <v>3</v>
       </c>
       <c r="C258" t="n">
-        <v>4213949.833669</v>
+        <v>8248327.516956</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>ES513</t>
+          <t>ES514</t>
         </is>
       </c>
       <c r="B259" t="n">
         <v>4</v>
       </c>
       <c r="C259" t="n">
-        <v>4567777.126897</v>
+        <v>8940904.200159</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>ES513</t>
+          <t>ES514</t>
         </is>
       </c>
       <c r="B260" t="n">
         <v>5</v>
       </c>
       <c r="C260" t="n">
-        <v>5075380.211858</v>
+        <v>9934479.505665001</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>ES513</t>
+          <t>ES514</t>
         </is>
       </c>
       <c r="B261" t="n">
         <v>6</v>
       </c>
       <c r="C261" t="n">
-        <v>5795353.29966</v>
+        <v>11343744.937384</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>ES513</t>
+          <t>ES514</t>
         </is>
       </c>
       <c r="B262" t="n">
         <v>7</v>
       </c>
       <c r="C262" t="n">
-        <v>6772437.539319</v>
+        <v>13256276.205784</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>ES514</t>
+          <t>ES521</t>
         </is>
       </c>
       <c r="B263" t="n">
         <v>1</v>
       </c>
       <c r="C263" t="n">
-        <v>7229025.88703</v>
+        <v>5795365.509489</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>ES514</t>
+          <t>ES521</t>
         </is>
       </c>
       <c r="B264" t="n">
         <v>2</v>
       </c>
       <c r="C264" t="n">
-        <v>7728471.858759</v>
+        <v>6195761.358617</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>ES514</t>
+          <t>ES521</t>
         </is>
       </c>
       <c r="B265" t="n">
         <v>3</v>
       </c>
       <c r="C265" t="n">
-        <v>8248327.516956</v>
+        <v>6612519.245296</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>ES514</t>
+          <t>ES521</t>
         </is>
       </c>
       <c r="B266" t="n">
         <v>4</v>
       </c>
       <c r="C266" t="n">
-        <v>8940904.200159</v>
+        <v>7167744.124172</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>ES514</t>
+          <t>ES521</t>
         </is>
       </c>
       <c r="B267" t="n">
         <v>5</v>
       </c>
       <c r="C267" t="n">
-        <v>9934479.505665001</v>
+        <v>7964273.580089</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>ES514</t>
+          <t>ES521</t>
         </is>
       </c>
       <c r="B268" t="n">
         <v>6</v>
       </c>
       <c r="C268" t="n">
-        <v>11343744.937384</v>
+        <v>9094053.498481</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>ES514</t>
+          <t>ES521</t>
         </is>
       </c>
       <c r="B269" t="n">
         <v>7</v>
       </c>
       <c r="C269" t="n">
-        <v>13256276.205784</v>
+        <v>10627291.575355</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>ES521</t>
+          <t>ES522</t>
         </is>
       </c>
       <c r="B270" t="n">
         <v>1</v>
       </c>
       <c r="C270" t="n">
-        <v>5795365.509489</v>
+        <v>5130334.14639</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>ES521</t>
+          <t>ES522</t>
         </is>
       </c>
       <c r="B271" t="n">
         <v>2</v>
       </c>
       <c r="C271" t="n">
-        <v>6195761.358617</v>
+        <v>5484783.661869</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>ES521</t>
+          <t>ES522</t>
         </is>
       </c>
       <c r="B272" t="n">
         <v>3</v>
       </c>
       <c r="C272" t="n">
-        <v>6612519.245296</v>
+        <v>5853717.633903</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>ES521</t>
+          <t>ES522</t>
         </is>
       </c>
       <c r="B273" t="n">
         <v>4</v>
       </c>
       <c r="C273" t="n">
-        <v>7167744.124172</v>
+        <v>6345229.196091</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>ES521</t>
+          <t>ES522</t>
         </is>
       </c>
       <c r="B274" t="n">
         <v>5</v>
       </c>
       <c r="C274" t="n">
-        <v>7964273.580089</v>
+        <v>7050355.086703</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>ES521</t>
+          <t>ES522</t>
         </is>
       </c>
       <c r="B275" t="n">
         <v>6</v>
       </c>
       <c r="C275" t="n">
-        <v>9094053.498481</v>
+        <v>8050490.191856</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>ES521</t>
+          <t>ES522</t>
         </is>
       </c>
       <c r="B276" t="n">
         <v>7</v>
       </c>
       <c r="C276" t="n">
-        <v>10627291.575355</v>
+        <v>9407785.714881999</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>ES522</t>
+          <t>ES523</t>
         </is>
       </c>
       <c r="B277" t="n">
         <v>1</v>
       </c>
       <c r="C277" t="n">
-        <v>5130334.14639</v>
+        <v>11568439.162262</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>ES522</t>
+          <t>ES523</t>
         </is>
       </c>
       <c r="B278" t="n">
         <v>2</v>
       </c>
       <c r="C278" t="n">
-        <v>5484783.661869</v>
+        <v>12367690.73904</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>ES522</t>
+          <t>ES523</t>
         </is>
       </c>
       <c r="B279" t="n">
         <v>3</v>
       </c>
       <c r="C279" t="n">
-        <v>5853717.633903</v>
+        <v>13199603.45439</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>ES522</t>
+          <t>ES523</t>
         </is>
       </c>
       <c r="B280" t="n">
         <v>4</v>
       </c>
       <c r="C280" t="n">
-        <v>6345229.196091</v>
+        <v>14307917.541245</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>ES522</t>
+          <t>ES523</t>
         </is>
       </c>
       <c r="B281" t="n">
         <v>5</v>
       </c>
       <c r="C281" t="n">
-        <v>7050355.086703</v>
+        <v>15897912.604826</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>ES522</t>
+          <t>ES523</t>
         </is>
       </c>
       <c r="B282" t="n">
         <v>6</v>
       </c>
       <c r="C282" t="n">
-        <v>8050490.191856</v>
+        <v>18153126.746412</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>ES522</t>
+          <t>ES523</t>
         </is>
       </c>
       <c r="B283" t="n">
         <v>7</v>
       </c>
       <c r="C283" t="n">
-        <v>9407785.714881999</v>
+        <v>21213705.30432</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>ES523</t>
+          <t>ES532</t>
         </is>
       </c>
       <c r="B284" t="n">
         <v>1</v>
       </c>
       <c r="C284" t="n">
-        <v>11568439.162262</v>
+        <v>3943784.055804</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>ES523</t>
+          <t>ES532</t>
         </is>
       </c>
       <c r="B285" t="n">
         <v>2</v>
       </c>
       <c r="C285" t="n">
-        <v>12367690.73904</v>
+        <v>4216256.044537</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>ES523</t>
+          <t>ES532</t>
         </is>
       </c>
       <c r="B286" t="n">
         <v>3</v>
       </c>
       <c r="C286" t="n">
-        <v>13199603.45439</v>
+        <v>4499862.506619</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>ES523</t>
+          <t>ES532</t>
         </is>
       </c>
       <c r="B287" t="n">
         <v>4</v>
       </c>
       <c r="C287" t="n">
-        <v>14307917.541245</v>
+        <v>4877696.66067</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>ES523</t>
+          <t>ES532</t>
         </is>
       </c>
       <c r="B288" t="n">
         <v>5</v>
       </c>
       <c r="C288" t="n">
-        <v>15897912.604826</v>
+        <v>5419740.154403</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>ES523</t>
+          <t>ES532</t>
         </is>
       </c>
       <c r="B289" t="n">
         <v>6</v>
       </c>
       <c r="C289" t="n">
-        <v>18153126.746412</v>
+        <v>6188562.76299</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>ES523</t>
+          <t>ES532</t>
         </is>
       </c>
       <c r="B290" t="n">
         <v>7</v>
       </c>
       <c r="C290" t="n">
-        <v>21213705.30432</v>
+        <v>7231941.281813</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>ES532</t>
+          <t>ES611</t>
         </is>
       </c>
       <c r="B291" t="n">
         <v>1</v>
       </c>
       <c r="C291" t="n">
-        <v>3943784.055804</v>
+        <v>3440996.322271</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>ES532</t>
+          <t>ES611</t>
         </is>
       </c>
       <c r="B292" t="n">
         <v>2</v>
       </c>
       <c r="C292" t="n">
-        <v>4216256.044537</v>
+        <v>3678731.223038</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>ES532</t>
+          <t>ES611</t>
         </is>
       </c>
       <c r="B293" t="n">
         <v>3</v>
       </c>
       <c r="C293" t="n">
-        <v>4499862.506619</v>
+        <v>3926181.078097</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>ES532</t>
+          <t>ES611</t>
         </is>
       </c>
       <c r="B294" t="n">
         <v>4</v>
       </c>
       <c r="C294" t="n">
-        <v>4877696.66067</v>
+        <v>4255845.663207</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>ES532</t>
+          <t>ES611</t>
         </is>
       </c>
       <c r="B295" t="n">
         <v>5</v>
       </c>
       <c r="C295" t="n">
-        <v>5419740.154403</v>
+        <v>4728784.759784</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>ES532</t>
+          <t>ES611</t>
         </is>
       </c>
       <c r="B296" t="n">
         <v>6</v>
       </c>
       <c r="C296" t="n">
-        <v>6188562.76299</v>
+        <v>5399591.206383</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>ES532</t>
+          <t>ES611</t>
         </is>
       </c>
       <c r="B297" t="n">
         <v>7</v>
       </c>
       <c r="C297" t="n">
-        <v>7231941.281813</v>
+        <v>6309950.798897</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>ES611</t>
+          <t>ES612</t>
         </is>
       </c>
       <c r="B298" t="n">
         <v>1</v>
       </c>
       <c r="C298" t="n">
-        <v>3440996.322271</v>
+        <v>4015299.176518</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>ES611</t>
+          <t>ES612</t>
         </is>
       </c>
       <c r="B299" t="n">
         <v>2</v>
       </c>
       <c r="C299" t="n">
-        <v>3678731.223038</v>
+        <v>4292712.07147</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>ES611</t>
+          <t>ES612</t>
         </is>
       </c>
       <c r="B300" t="n">
         <v>3</v>
       </c>
       <c r="C300" t="n">
-        <v>3926181.078097</v>
+        <v>4581461.348189</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>ES611</t>
+          <t>ES612</t>
         </is>
       </c>
       <c r="B301" t="n">
         <v>4</v>
       </c>
       <c r="C301" t="n">
-        <v>4255845.663207</v>
+        <v>4966147.006976</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>ES611</t>
+          <t>ES612</t>
         </is>
       </c>
       <c r="B302" t="n">
         <v>5</v>
       </c>
       <c r="C302" t="n">
-        <v>4728784.759784</v>
+        <v>5518019.716848</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>ES611</t>
+          <t>ES612</t>
         </is>
       </c>
       <c r="B303" t="n">
         <v>6</v>
       </c>
       <c r="C303" t="n">
-        <v>5399591.206383</v>
+        <v>6300783.870125</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>ES611</t>
+          <t>ES612</t>
         </is>
       </c>
       <c r="B304" t="n">
         <v>7</v>
       </c>
       <c r="C304" t="n">
-        <v>6309950.798897</v>
+        <v>7363082.628918</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>ES612</t>
+          <t>ES613</t>
         </is>
       </c>
       <c r="B305" t="n">
         <v>1</v>
       </c>
       <c r="C305" t="n">
-        <v>4015299.176518</v>
+        <v>2276648.591564</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>ES612</t>
+          <t>ES613</t>
         </is>
       </c>
       <c r="B306" t="n">
         <v>2</v>
       </c>
       <c r="C306" t="n">
-        <v>4292712.07147</v>
+        <v>2433939.903819</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>ES612</t>
+          <t>ES613</t>
         </is>
       </c>
       <c r="B307" t="n">
         <v>3</v>
       </c>
       <c r="C307" t="n">
-        <v>4581461.348189</v>
+        <v>2597658.871014</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>ES612</t>
+          <t>ES613</t>
         </is>
       </c>
       <c r="B308" t="n">
         <v>4</v>
       </c>
       <c r="C308" t="n">
-        <v>4966147.006976</v>
+        <v>2815773.144639</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>ES612</t>
+          <t>ES613</t>
         </is>
       </c>
       <c r="B309" t="n">
         <v>5</v>
       </c>
       <c r="C309" t="n">
-        <v>5518019.716848</v>
+        <v>3128681.391925</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>ES612</t>
+          <t>ES613</t>
         </is>
       </c>
       <c r="B310" t="n">
         <v>6</v>
       </c>
       <c r="C310" t="n">
-        <v>6300783.870125</v>
+        <v>3572503.590158</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>ES612</t>
+          <t>ES613</t>
         </is>
       </c>
       <c r="B311" t="n">
         <v>7</v>
       </c>
       <c r="C311" t="n">
-        <v>7363082.628918</v>
+        <v>4174820.096775</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>ES613</t>
+          <t>ES614</t>
         </is>
       </c>
       <c r="B312" t="n">
         <v>1</v>
       </c>
       <c r="C312" t="n">
-        <v>2276648.591564</v>
+        <v>3869397.043576</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>ES613</t>
+          <t>ES614</t>
         </is>
       </c>
       <c r="B313" t="n">
         <v>2</v>
       </c>
       <c r="C313" t="n">
-        <v>2433939.903819</v>
+        <v>4136729.710057</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>ES613</t>
+          <t>ES614</t>
         </is>
       </c>
       <c r="B314" t="n">
         <v>3</v>
       </c>
       <c r="C314" t="n">
-        <v>2597658.871014</v>
+        <v>4414986.833264</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>ES613</t>
+          <t>ES614</t>
         </is>
       </c>
       <c r="B315" t="n">
         <v>4</v>
       </c>
       <c r="C315" t="n">
-        <v>2815773.144639</v>
+        <v>4785694.341068</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>ES613</t>
+          <t>ES614</t>
         </is>
       </c>
       <c r="B316" t="n">
         <v>5</v>
       </c>
       <c r="C316" t="n">
-        <v>3128681.391925</v>
+        <v>5317513.898748</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>ES613</t>
+          <t>ES614</t>
         </is>
       </c>
       <c r="B317" t="n">
         <v>6</v>
       </c>
       <c r="C317" t="n">
-        <v>3572503.590158</v>
+        <v>6071835.10057</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>ES613</t>
+          <t>ES614</t>
         </is>
       </c>
       <c r="B318" t="n">
         <v>7</v>
       </c>
       <c r="C318" t="n">
-        <v>4174820.096775</v>
+        <v>7095533.583788</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>ES614</t>
+          <t>ES615</t>
         </is>
       </c>
       <c r="B319" t="n">
         <v>1</v>
       </c>
       <c r="C319" t="n">
-        <v>3869397.043576</v>
+        <v>2989656.18877</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>ES614</t>
+          <t>ES615</t>
         </is>
       </c>
       <c r="B320" t="n">
         <v>2</v>
       </c>
       <c r="C320" t="n">
-        <v>4136729.710057</v>
+        <v>3196208.463401</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>ES614</t>
+          <t>ES615</t>
         </is>
       </c>
       <c r="B321" t="n">
         <v>3</v>
       </c>
       <c r="C321" t="n">
-        <v>4414986.833264</v>
+        <v>3411201.42512</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>ES614</t>
+          <t>ES615</t>
         </is>
       </c>
       <c r="B322" t="n">
         <v>4</v>
       </c>
       <c r="C322" t="n">
-        <v>4785694.341068</v>
+        <v>3697625.377599</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>ES614</t>
+          <t>ES615</t>
         </is>
       </c>
       <c r="B323" t="n">
         <v>5</v>
       </c>
       <c r="C323" t="n">
-        <v>5317513.898748</v>
+        <v>4108531.163183</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>ES614</t>
+          <t>ES615</t>
         </is>
       </c>
       <c r="B324" t="n">
         <v>6</v>
       </c>
       <c r="C324" t="n">
-        <v>6071835.10057</v>
+        <v>4691350.921391</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>ES614</t>
+          <t>ES615</t>
         </is>
       </c>
       <c r="B325" t="n">
         <v>7</v>
       </c>
       <c r="C325" t="n">
-        <v>7095533.583788</v>
+        <v>5482302.708276</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>ES615</t>
+          <t>ES616</t>
         </is>
       </c>
       <c r="B326" t="n">
         <v>1</v>
       </c>
       <c r="C326" t="n">
-        <v>2989656.18877</v>
+        <v>2338999.220812</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>ES615</t>
+          <t>ES616</t>
         </is>
       </c>
       <c r="B327" t="n">
         <v>2</v>
       </c>
       <c r="C327" t="n">
-        <v>3196208.463401</v>
+        <v>2500598.273986</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>ES615</t>
+          <t>ES616</t>
         </is>
       </c>
       <c r="B328" t="n">
         <v>3</v>
       </c>
       <c r="C328" t="n">
-        <v>3411201.42512</v>
+        <v>2668801.016438</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>ES615</t>
+          <t>ES616</t>
         </is>
       </c>
       <c r="B329" t="n">
         <v>4</v>
       </c>
       <c r="C329" t="n">
-        <v>3697625.377599</v>
+        <v>2892888.790874</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>ES615</t>
+          <t>ES616</t>
         </is>
       </c>
       <c r="B330" t="n">
         <v>5</v>
       </c>
       <c r="C330" t="n">
-        <v>4108531.163183</v>
+        <v>3214366.663787</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>ES615</t>
+          <t>ES616</t>
         </is>
       </c>
       <c r="B331" t="n">
         <v>6</v>
       </c>
       <c r="C331" t="n">
-        <v>4691350.921391</v>
+        <v>3670343.831143</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>ES615</t>
+          <t>ES616</t>
         </is>
       </c>
       <c r="B332" t="n">
         <v>7</v>
       </c>
       <c r="C332" t="n">
-        <v>5482302.708276</v>
+        <v>4289155.994285</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>ES616</t>
+          <t>ES617</t>
         </is>
       </c>
       <c r="B333" t="n">
         <v>1</v>
       </c>
       <c r="C333" t="n">
-        <v>2338999.220812</v>
+        <v>4856250.096158</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>ES616</t>
+          <t>ES617</t>
         </is>
       </c>
       <c r="B334" t="n">
         <v>2</v>
       </c>
       <c r="C334" t="n">
-        <v>2500598.273986</v>
+        <v>5191763.426188</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>ES616</t>
+          <t>ES617</t>
         </is>
       </c>
       <c r="B335" t="n">
         <v>3</v>
       </c>
       <c r="C335" t="n">
-        <v>2668801.016438</v>
+        <v>5540987.392122</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>ES616</t>
+          <t>ES617</t>
         </is>
       </c>
       <c r="B336" t="n">
         <v>4</v>
       </c>
       <c r="C336" t="n">
-        <v>2892888.790874</v>
+        <v>6006240.337258</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>ES616</t>
+          <t>ES617</t>
         </is>
       </c>
       <c r="B337" t="n">
         <v>5</v>
       </c>
       <c r="C337" t="n">
-        <v>3214366.663787</v>
+        <v>6673695.434017</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>ES616</t>
+          <t>ES617</t>
         </is>
       </c>
       <c r="B338" t="n">
         <v>6</v>
       </c>
       <c r="C338" t="n">
-        <v>3670343.831143</v>
+        <v>7620399.111006</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>ES616</t>
+          <t>ES617</t>
         </is>
       </c>
       <c r="B339" t="n">
         <v>7</v>
       </c>
       <c r="C339" t="n">
-        <v>4289155.994285</v>
+        <v>8905182.192601001</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>ES617</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B340" t="n">
         <v>1</v>
       </c>
       <c r="C340" t="n">
-        <v>4856250.096158</v>
+        <v>6965774.361604</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>ES617</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B341" t="n">
         <v>2</v>
       </c>
       <c r="C341" t="n">
-        <v>5191763.426188</v>
+        <v>7447032.555895</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>ES617</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B342" t="n">
         <v>3</v>
       </c>
       <c r="C342" t="n">
-        <v>5540987.392122</v>
+        <v>7947957.199435</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>ES617</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B343" t="n">
         <v>4</v>
       </c>
       <c r="C343" t="n">
-        <v>6006240.337258</v>
+        <v>8615313.075412</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>ES617</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B344" t="n">
         <v>5</v>
       </c>
       <c r="C344" t="n">
-        <v>6673695.434017</v>
+        <v>9572706.43623</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>ES617</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B345" t="n">
         <v>6</v>
       </c>
       <c r="C345" t="n">
-        <v>7620399.111006</v>
+        <v>10930652.190799</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>ES617</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B346" t="n">
         <v>7</v>
       </c>
       <c r="C346" t="n">
-        <v>8905182.192601001</v>
+        <v>12773536.900769</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>ES618</t>
+          <t>ES620</t>
         </is>
       </c>
       <c r="B347" t="n">
         <v>1</v>
       </c>
       <c r="C347" t="n">
-        <v>6965774.361604</v>
+        <v>5650432.983876</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>ES618</t>
+          <t>ES620</t>
         </is>
       </c>
       <c r="B348" t="n">
         <v>2</v>
       </c>
       <c r="C348" t="n">
-        <v>7447032.555895</v>
+        <v>6040815.593708</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>ES618</t>
+          <t>ES620</t>
         </is>
       </c>
       <c r="B349" t="n">
         <v>3</v>
       </c>
       <c r="C349" t="n">
-        <v>7947957.199435</v>
+        <v>6447151.053538</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>ES618</t>
+          <t>ES620</t>
         </is>
       </c>
       <c r="B350" t="n">
         <v>4</v>
       </c>
       <c r="C350" t="n">
-        <v>8615313.075412</v>
+        <v>6988490.674642</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>ES618</t>
+          <t>ES620</t>
         </is>
       </c>
       <c r="B351" t="n">
         <v>5</v>
       </c>
       <c r="C351" t="n">
-        <v>9572706.43623</v>
+        <v>7765100.243612</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>ES618</t>
+          <t>ES620</t>
         </is>
       </c>
       <c r="B352" t="n">
         <v>6</v>
       </c>
       <c r="C352" t="n">
-        <v>10930652.190799</v>
+        <v>8866626.231048999</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>ES618</t>
+          <t>ES620</t>
         </is>
       </c>
       <c r="B353" t="n">
         <v>7</v>
       </c>
       <c r="C353" t="n">
-        <v>12773536.900769</v>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>ES620</t>
-        </is>
-      </c>
-      <c r="B354" t="n">
-        <v>1</v>
-      </c>
-      <c r="C354" t="n">
-        <v>5650432.983876</v>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>ES620</t>
-        </is>
-      </c>
-      <c r="B355" t="n">
-        <v>2</v>
-      </c>
-      <c r="C355" t="n">
-        <v>6040815.593708</v>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>ES620</t>
-        </is>
-      </c>
-      <c r="B356" t="n">
-        <v>3</v>
-      </c>
-      <c r="C356" t="n">
-        <v>6447151.053538</v>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>ES620</t>
-        </is>
-      </c>
-      <c r="B357" t="n">
-        <v>4</v>
-      </c>
-      <c r="C357" t="n">
-        <v>6988490.674642</v>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>ES620</t>
-        </is>
-      </c>
-      <c r="B358" t="n">
-        <v>5</v>
-      </c>
-      <c r="C358" t="n">
-        <v>7765100.243612</v>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>ES620</t>
-        </is>
-      </c>
-      <c r="B359" t="n">
-        <v>6</v>
-      </c>
-      <c r="C359" t="n">
-        <v>8866626.231048999</v>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>ES620</t>
-        </is>
-      </c>
-      <c r="B360" t="n">
-        <v>7</v>
-      </c>
-      <c r="C360" t="n">
         <v>10361520.55437</v>
       </c>
     </row>
@@ -5105,7 +5014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5159,7 +5068,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -5172,7 +5081,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -5185,7 +5094,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5198,7 +5107,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES112</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5211,7 +5120,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ES112</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5224,7 +5133,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES114</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -5237,7 +5146,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ES114</t>
+          <t>ES120</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -5250,7 +5159,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ES120</t>
+          <t>ES130</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -5263,7 +5172,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ES130</t>
+          <t>ES211</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -5276,7 +5185,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ES211</t>
+          <t>ES212</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -5289,7 +5198,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ES212</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -5302,7 +5211,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ES213</t>
+          <t>ES220</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -5315,7 +5224,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ES220</t>
+          <t>ES230</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -5328,7 +5237,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ES230</t>
+          <t>ES241</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -5341,7 +5250,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ES241</t>
+          <t>ES242</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -5354,7 +5263,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ES242</t>
+          <t>ES243</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -5367,7 +5276,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ES243</t>
+          <t>ES300</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -5380,7 +5289,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ES300</t>
+          <t>ES412</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -5393,7 +5302,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ES412</t>
+          <t>ES413</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -5406,7 +5315,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ES413</t>
+          <t>ES414</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -5419,7 +5328,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ES414</t>
+          <t>ES415</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -5432,7 +5341,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ES415</t>
+          <t>ES416</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -5445,7 +5354,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ES416</t>
+          <t>ES417</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -5458,7 +5367,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ES417</t>
+          <t>ES418</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -5471,7 +5380,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ES418</t>
+          <t>ES419</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -5484,7 +5393,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ES419</t>
+          <t>ES421</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -5497,7 +5406,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ES421</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -5510,7 +5419,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES423</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -5523,7 +5432,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ES423</t>
+          <t>ES424</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -5536,7 +5445,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ES424</t>
+          <t>ES425</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -5549,7 +5458,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ES425</t>
+          <t>ES431</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -5562,7 +5471,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ES431</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -5575,7 +5484,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>ES511</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -5588,7 +5497,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ES511</t>
+          <t>ES512</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -5601,7 +5510,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ES512</t>
+          <t>ES513</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -5614,7 +5523,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ES513</t>
+          <t>ES514</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -5627,7 +5536,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ES514</t>
+          <t>ES521</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -5640,7 +5549,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ES521</t>
+          <t>ES522</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -5653,7 +5562,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ES522</t>
+          <t>ES523</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -5666,7 +5575,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ES523</t>
+          <t>ES532</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -5679,7 +5588,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ES532</t>
+          <t>ES611</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -5692,7 +5601,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ES611</t>
+          <t>ES612</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -5705,7 +5614,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ES612</t>
+          <t>ES613</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -5718,7 +5627,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ES613</t>
+          <t>ES614</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -5731,7 +5640,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ES614</t>
+          <t>ES615</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -5744,7 +5653,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ES615</t>
+          <t>ES616</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -5757,7 +5666,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ES616</t>
+          <t>ES617</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -5770,7 +5679,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ES617</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -5783,26 +5692,13 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ES618</t>
+          <t>ES620</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>ES620</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>1</v>
-      </c>
-      <c r="C54" t="n">
         <v>22000</v>
       </c>
     </row>
@@ -5817,7 +5713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B54"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5861,37 +5757,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>44940000</v>
+        <v>16050000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16050000</v>
+        <v>485576700</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>ES111</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>440636700</v>
+        <v>956170.213</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ES111</t>
+          <t>ES112</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5901,7 +5797,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ES112</t>
+          <t>ES113</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5911,7 +5807,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ES113</t>
+          <t>ES114</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -5921,7 +5817,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ES114</t>
+          <t>ES120</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -5931,7 +5827,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ES120</t>
+          <t>ES130</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -5941,7 +5837,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ES130</t>
+          <t>ES211</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -5951,7 +5847,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ES211</t>
+          <t>ES212</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -5961,7 +5857,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ES212</t>
+          <t>ES213</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -5971,7 +5867,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ES213</t>
+          <t>ES220</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -5981,7 +5877,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ES220</t>
+          <t>ES230</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -5991,7 +5887,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ES230</t>
+          <t>ES241</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -6001,7 +5897,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ES241</t>
+          <t>ES242</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -6011,7 +5907,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ES242</t>
+          <t>ES243</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -6021,7 +5917,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ES243</t>
+          <t>ES300</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -6031,7 +5927,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ES300</t>
+          <t>ES412</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -6041,7 +5937,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ES412</t>
+          <t>ES413</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -6051,7 +5947,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ES413</t>
+          <t>ES414</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -6061,7 +5957,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ES414</t>
+          <t>ES415</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -6071,7 +5967,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ES415</t>
+          <t>ES416</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -6081,7 +5977,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ES416</t>
+          <t>ES417</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -6091,7 +5987,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ES417</t>
+          <t>ES418</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -6101,7 +5997,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ES418</t>
+          <t>ES419</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -6111,7 +6007,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ES419</t>
+          <t>ES421</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -6121,7 +6017,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ES421</t>
+          <t>ES422</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -6131,7 +6027,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ES422</t>
+          <t>ES423</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -6141,7 +6037,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ES423</t>
+          <t>ES424</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -6151,7 +6047,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ES424</t>
+          <t>ES425</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -6161,7 +6057,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ES425</t>
+          <t>ES431</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -6171,7 +6067,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ES431</t>
+          <t>ES432</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -6181,7 +6077,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ES432</t>
+          <t>ES511</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -6191,7 +6087,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ES511</t>
+          <t>ES512</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -6201,7 +6097,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ES512</t>
+          <t>ES513</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -6211,7 +6107,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ES513</t>
+          <t>ES514</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -6221,7 +6117,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ES514</t>
+          <t>ES521</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -6231,7 +6127,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ES521</t>
+          <t>ES522</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -6241,7 +6137,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ES522</t>
+          <t>ES523</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -6251,7 +6147,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ES523</t>
+          <t>ES532</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -6261,7 +6157,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ES532</t>
+          <t>ES611</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -6271,7 +6167,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ES611</t>
+          <t>ES612</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -6281,7 +6177,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ES612</t>
+          <t>ES613</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -6291,7 +6187,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ES613</t>
+          <t>ES614</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -6301,7 +6197,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ES614</t>
+          <t>ES615</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -6311,7 +6207,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ES615</t>
+          <t>ES616</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -6321,7 +6217,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ES616</t>
+          <t>ES617</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -6331,7 +6227,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ES617</t>
+          <t>ES618</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -6341,20 +6237,10 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ES618</t>
+          <t>ES620</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>956170.213</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>ES620</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
         <v>956170.213</v>
       </c>
     </row>
